--- a/artfynd/A 39365-2024 artfynd.xlsx
+++ b/artfynd/A 39365-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103401907</v>
+        <v>103401896</v>
       </c>
       <c r="B2" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551980.7896166049</v>
+        <v>552074</v>
       </c>
       <c r="R2" t="n">
-        <v>7016904.804605708</v>
+        <v>7016935</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103401906</v>
+        <v>103995950</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551808.5207926333</v>
+        <v>552133</v>
       </c>
       <c r="R3" t="n">
-        <v>7016853.409015231</v>
+        <v>7016922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,31 +863,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103401905</v>
+        <v>103401902</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551820.3190381646</v>
+        <v>551943</v>
       </c>
       <c r="R4" t="n">
-        <v>7016876.557312888</v>
+        <v>7016888</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +956,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +985,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103401908</v>
+        <v>103995967</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551817.6427268988</v>
+        <v>552134</v>
       </c>
       <c r="R5" t="n">
-        <v>7016846.803409159</v>
+        <v>7016912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1050,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,31 +1076,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103995926</v>
+        <v>103401894</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552112.0842784337</v>
+        <v>552055</v>
       </c>
       <c r="R6" t="n">
-        <v>7016869.56476309</v>
+        <v>7016980</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1166,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,62 +1182,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103995967</v>
+        <v>103401900</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552133.9391622175</v>
+        <v>551939</v>
       </c>
       <c r="R7" t="n">
-        <v>7016911.783758349</v>
+        <v>7016897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,22 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,40 +1279,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103995952</v>
+        <v>103401906</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>551825.3342634746</v>
+        <v>551809</v>
       </c>
       <c r="R8" t="n">
-        <v>7016873.036784383</v>
+        <v>7016854</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,22 +1360,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,62 +1376,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103995920</v>
+        <v>103401909</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552112.069702159</v>
+        <v>551743</v>
       </c>
       <c r="R9" t="n">
-        <v>7016870.464855175</v>
+        <v>7017064</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,22 +1457,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2022-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,24 +1473,1660 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>103995865</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>551941</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7016898</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103995927</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552072</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7016971</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103401898</v>
+      </c>
+      <c r="B12" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>551923</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7016896</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>103995888</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>552059</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7016979</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>103995952</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>551825</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7016873</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103401904</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>551887</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7016872</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>103401905</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>551820</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7016877</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>103995896</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>551940</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7016877</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>103995920</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>552112</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7016871</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>103995869</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>551940</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7016882</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>103995915</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>551908</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7017010</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>103401907</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>551981</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7016905</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>103401908</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>551818</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7016847</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>103995832</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>551937</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7016869</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>103995926</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fågelleksmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>552112</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7016869</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-07-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 39365-2024 artfynd.xlsx
+++ b/artfynd/A 39365-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995950</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401902</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995967</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401900</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401906</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995865</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995927</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401898</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995888</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2047,6 +2112,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995952</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2144,6 +2214,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401904</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2241,6 +2316,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401905</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2357,6 +2437,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995896</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2473,6 +2558,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995920</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2589,6 +2679,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995869</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995915</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401907</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,6 +3004,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401908</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995832</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3131,8 +3246,38 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995926</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>